--- a/Projects/Datasets for Excel/Datasets for excel/filtering+data.xlsx
+++ b/Projects/Datasets for Excel/Datasets for excel/filtering+data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shahriar/Desktop/PROJECTs/Course/Data - Excel/6. filtering/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DS\tezendra\Projects\Datasets for Excel\Datasets for excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31A9B316-CE17-D246-B5B1-E811C0FB543B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1DD7B6-9427-4274-B3C6-030A065936B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{46B74526-A74E-6046-9D0E-2CEB55D79120}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="16520" xr2:uid="{46B74526-A74E-6046-9D0E-2CEB55D79120}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -337,9 +337,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -377,7 +377,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -483,7 +483,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -625,7 +625,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -633,17 +633,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40BF641-9A5E-7143-93C1-2643454410EF}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -660,7 +661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -677,7 +678,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -694,7 +695,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -711,7 +712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -728,7 +729,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -745,7 +746,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>42</v>
       </c>
@@ -762,7 +763,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -779,7 +780,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>65</v>
       </c>
@@ -796,7 +797,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -813,7 +814,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -830,7 +831,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -847,7 +848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -864,7 +865,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -881,7 +882,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -898,7 +899,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -915,7 +916,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>77</v>
       </c>
@@ -932,7 +933,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -949,7 +950,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>66</v>
       </c>
@@ -966,7 +967,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -983,7 +984,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1000,7 +1001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -1017,7 +1018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -1034,7 +1035,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -1051,7 +1052,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>74</v>
       </c>
@@ -1068,7 +1069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -1085,7 +1086,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -1102,7 +1103,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -1119,7 +1120,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -1136,7 +1137,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>73</v>
       </c>
@@ -1153,7 +1154,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -1170,7 +1171,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -1187,7 +1188,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -1204,7 +1205,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -1221,7 +1222,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -1238,7 +1239,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -1255,7 +1256,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>52</v>
       </c>
@@ -1272,7 +1273,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -1289,7 +1290,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>60</v>
       </c>
@@ -1306,7 +1307,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>62</v>
       </c>
@@ -1323,7 +1324,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>72</v>
       </c>
@@ -1340,7 +1341,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1357,7 +1358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -1374,7 +1375,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -1391,7 +1392,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -1408,7 +1409,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>36</v>
       </c>
@@ -1425,7 +1426,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -1442,7 +1443,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>29</v>
       </c>
@@ -1459,7 +1460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>67</v>
       </c>
@@ -1476,7 +1477,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>76</v>
       </c>
@@ -1493,7 +1494,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>75</v>
       </c>
@@ -1511,7 +1512,23 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E51" xr:uid="{D40BF641-9A5E-7143-93C1-2643454410EF}"/>
+  <autoFilter ref="A1:E51" xr:uid="{D40BF641-9A5E-7143-93C1-2643454410EF}">
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="greaterThanOrEqual" val="30"/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Male"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="San Antonio"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>